--- a/Penman_irrigation_summary.xlsx
+++ b/Penman_irrigation_summary.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:R54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3433,6 +3433,36 @@
         <v>19.4368</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Penman_irrigation_summary.xlsx
+++ b/Penman_irrigation_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Penman_irrigation_summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Penman_irrigation_summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R54"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,71 +3397,153 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.1944</v>
+        <v>0.172</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.5486</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5604</v>
+        <v>0.538</v>
       </c>
       <c r="J53" t="n">
-        <v>0.1803</v>
+        <v>0.1598</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1944</v>
+        <v>0.172</v>
       </c>
       <c r="L53" t="n">
-        <v>1.0146</v>
+        <v>0.9941</v>
       </c>
       <c r="M53" t="n">
-        <v>3.7245</v>
+        <v>3.2946</v>
       </c>
       <c r="N53" t="n">
-        <v>10.9017</v>
+        <v>10.5091</v>
       </c>
       <c r="O53" t="n">
-        <v>10.7358</v>
+        <v>10.3058</v>
       </c>
       <c r="P53" t="n">
-        <v>3.4534</v>
+        <v>3.0608</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.7245</v>
+        <v>3.2946</v>
       </c>
       <c r="R53" t="n">
-        <v>19.4368</v>
+        <v>19.0442</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
         <v>45475</v>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.0912</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>0.0912</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.7417</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.6582</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.1872</v>
+      </c>
+      <c r="M54" t="n">
+        <v>5.5985</v>
+      </c>
+      <c r="N54" t="n">
+        <v>14.2079</v>
+      </c>
+      <c r="O54" t="n">
+        <v>12.6098</v>
+      </c>
+      <c r="P54" t="n">
+        <v>6.7596</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>7.3456</v>
+      </c>
+      <c r="R54" t="n">
+        <v>22.743</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45476</v>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.8213</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.7454</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.4706</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.1804</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>15.7329</v>
+      </c>
+      <c r="O55" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="P55" t="n">
+        <v>8.284599999999999</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>9.0159</v>
+      </c>
+      <c r="R55" t="n">
+        <v>22.6128</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
